--- a/verification/cases/roundtrip/formulas_text/init.xlsx
+++ b/verification/cases/roundtrip/formulas_text/init.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/text/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79B6A69-2A52-2E4A-8886-25067EFFA474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4E3A57D-E0DB-43DF-B6B3-881D2ED78D86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="660" windowWidth="27900" windowHeight="15100" xr2:uid="{330BF130-502A-564A-8CF7-869F08690EB6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{330BF130-502A-564A-8CF7-869F08690EB6}"/>
   </bookViews>
   <sheets>
     <sheet name="Text Functions" sheetId="1" r:id="rId1"/>
@@ -756,7 +756,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+  <wetp:taskpane dockstate="right" visibility="1" width="438" row="0">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -779,26 +779,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76059F98-D522-B74B-BA80-08925E4CCC64}">
   <dimension ref="B2:L190"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="38.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="21.1640625" customWidth="1"/>
-    <col min="5" max="5" width="23.33203125" customWidth="1"/>
+    <col min="4" max="4" width="21.19921875" customWidth="1"/>
+    <col min="5" max="5" width="23.296875" customWidth="1"/>
     <col min="6" max="6" width="24.5" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="21.33203125" customWidth="1"/>
-    <col min="9" max="9" width="22.33203125" customWidth="1"/>
-    <col min="10" max="10" width="21.1640625" customWidth="1"/>
+    <col min="8" max="8" width="21.296875" customWidth="1"/>
+    <col min="9" max="9" width="22.296875" customWidth="1"/>
+    <col min="10" max="10" width="21.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="19" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" ht="18" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="L2" s="15"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -810,12 +810,12 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
@@ -824,7 +824,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
@@ -832,7 +832,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
@@ -840,7 +840,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
@@ -848,7 +848,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="8">
         <v>123</v>
       </c>
@@ -856,7 +856,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
@@ -864,7 +864,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
@@ -872,7 +872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="32" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>10</v>
       </c>
@@ -882,7 +882,7 @@
 Break</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -894,7 +894,7 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>11</v>
       </c>
@@ -908,7 +908,7 @@
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="11" t="s">
         <v>1</v>
       </c>
@@ -937,7 +937,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="5" t="s">
         <v>4</v>
       </c>
@@ -975,7 +975,7 @@
 Break</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="5" t="s">
         <v>5</v>
       </c>
@@ -1013,7 +1013,7 @@
 Break</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="5" t="s">
         <v>6</v>
       </c>
@@ -1051,7 +1051,7 @@
 Break</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="5" t="s">
         <v>7</v>
       </c>
@@ -1089,7 +1089,7 @@
 Break</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="5">
         <v>123</v>
       </c>
@@ -1127,7 +1127,7 @@
 Break</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
@@ -1165,7 +1165,7 @@
 Break</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="5" t="s">
         <v>9</v>
       </c>
@@ -1203,7 +1203,7 @@
 Break</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="5" t="s">
         <v>12</v>
       </c>
@@ -1249,7 +1249,7 @@
 Break</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="14" t="s">
         <v>13</v>
       </c>
@@ -1263,7 +1263,7 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="11" t="s">
         <v>1</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="5" t="s">
         <v>4</v>
       </c>
@@ -1330,7 +1330,7 @@
 Break</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" s="5" t="s">
         <v>5</v>
       </c>
@@ -1368,7 +1368,7 @@
 Break</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30" s="5" t="s">
         <v>6</v>
       </c>
@@ -1406,7 +1406,7 @@
 Break</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31" s="5" t="s">
         <v>7</v>
       </c>
@@ -1444,7 +1444,7 @@
 Break</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="5">
         <v>123</v>
       </c>
@@ -1482,7 +1482,7 @@
 Break</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33" s="5" t="s">
         <v>8</v>
       </c>
@@ -1520,7 +1520,7 @@
 Break</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B34" s="5" t="s">
         <v>9</v>
       </c>
@@ -1558,7 +1558,7 @@
 Break</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" s="5" t="s">
         <v>12</v>
       </c>
@@ -1604,7 +1604,7 @@
 Break</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B37" s="14" t="s">
         <v>14</v>
       </c>
@@ -1618,7 +1618,7 @@
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B38" s="11" t="s">
         <v>1</v>
       </c>
@@ -1647,7 +1647,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B39" s="5" t="s">
         <v>4</v>
       </c>
@@ -1685,7 +1685,7 @@
 Break</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B40" s="5" t="s">
         <v>5</v>
       </c>
@@ -1723,7 +1723,7 @@
 Break</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B41" s="5" t="s">
         <v>6</v>
       </c>
@@ -1761,7 +1761,7 @@
 Break</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B42" s="5" t="s">
         <v>7</v>
       </c>
@@ -1799,7 +1799,7 @@
 Break</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B43" s="5">
         <v>123</v>
       </c>
@@ -1837,7 +1837,7 @@
 Break</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B44" s="5" t="s">
         <v>8</v>
       </c>
@@ -1875,7 +1875,7 @@
 Break</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B45" s="5" t="s">
         <v>9</v>
       </c>
@@ -1913,7 +1913,7 @@
 Break</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B46" s="5" t="s">
         <v>12</v>
       </c>
@@ -1959,7 +1959,7 @@
 Break</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B48" s="14" t="s">
         <v>15</v>
       </c>
@@ -1973,7 +1973,7 @@
       <c r="J48" s="4"/>
       <c r="K48" s="4"/>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B49" s="11" t="s">
         <v>16</v>
       </c>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="H49" s="12"/>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B50" s="5" t="s">
         <v>4</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B51" s="5" t="s">
         <v>5</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>Hello</v>
       </c>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B52" s="5" t="s">
         <v>6</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>hello world</v>
       </c>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B53" s="5" t="s">
         <v>7</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v xml:space="preserve">  Hello World  </v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B54" s="5">
         <v>123</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B55" s="5" t="s">
         <v>8</v>
       </c>
@@ -2144,7 +2144,7 @@
         <v>Hello123</v>
       </c>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B56" s="5" t="s">
         <v>9</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>A&amp;B@C</v>
       </c>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B57" s="5" t="s">
         <v>12</v>
       </c>
@@ -2197,7 +2197,7 @@
 Break</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B59" s="14" t="s">
         <v>17</v>
       </c>
@@ -2211,7 +2211,7 @@
       <c r="J59" s="4"/>
       <c r="K59" s="4"/>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B60" s="11" t="s">
         <v>16</v>
       </c>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H60" s="12"/>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B61" s="5" t="s">
         <v>4</v>
       </c>
@@ -2257,7 +2257,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B62" s="5" t="s">
         <v>5</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>Hello</v>
       </c>
     </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B63" s="5" t="s">
         <v>6</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>hello world</v>
       </c>
     </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B64" s="5" t="s">
         <v>7</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v xml:space="preserve">  Hello World  </v>
       </c>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B65" s="5">
         <v>123</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B66" s="5" t="s">
         <v>8</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>Hello123</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B67" s="5" t="s">
         <v>9</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>A&amp;B@C</v>
       </c>
     </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B68" s="5" t="s">
         <v>12</v>
       </c>
@@ -2434,7 +2434,7 @@
 Break</v>
       </c>
     </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B70" s="14" t="s">
         <v>18</v>
       </c>
@@ -2448,7 +2448,7 @@
       <c r="J70" s="4"/>
       <c r="K70" s="4"/>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B71" s="11" t="s">
         <v>19</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B72" s="5" t="s">
         <v>4</v>
       </c>
@@ -2507,7 +2507,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B73" s="5" t="s">
         <v>5</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B74" s="5" t="s">
         <v>6</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>world</v>
       </c>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B75" s="5" t="s">
         <v>7</v>
       </c>
@@ -2606,7 +2606,7 @@
         <v>o Wor</v>
       </c>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B76" s="5">
         <v>123</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B77" s="5" t="s">
         <v>8</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B78" s="5" t="s">
         <v>9</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B79" s="5" t="s">
         <v>12</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>reak</v>
       </c>
     </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B81" s="14" t="s">
         <v>26</v>
       </c>
@@ -2755,7 +2755,7 @@
       <c r="J81" s="4"/>
       <c r="K81" s="4"/>
     </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B83" s="10" t="s">
         <v>2</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B84" s="5" t="s">
         <v>4</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="5" t="s">
         <v>5</v>
       </c>
@@ -2836,7 +2836,7 @@
         <v>Hello</v>
       </c>
     </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B86" s="5" t="s">
         <v>6</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>Hello World</v>
       </c>
     </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B87" s="5" t="s">
         <v>7</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v xml:space="preserve">  Hello World  </v>
       </c>
     </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="5">
         <v>123</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="5" t="s">
         <v>8</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>Hello123</v>
       </c>
     </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="5" t="s">
         <v>9</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>A&amp;B@C</v>
       </c>
     </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B91" s="5" t="s">
         <v>12</v>
       </c>
@@ -3014,7 +3014,7 @@
 Break</v>
       </c>
     </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="14" t="s">
         <v>33</v>
       </c>
@@ -3028,7 +3028,7 @@
       <c r="J93" s="4"/>
       <c r="K93" s="4"/>
     </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B94" s="11" t="s">
         <v>34</v>
       </c>
@@ -3054,7 +3054,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="5" t="s">
         <v>4</v>
       </c>
@@ -3087,7 +3087,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B96" s="5" t="s">
         <v>5</v>
       </c>
@@ -3120,7 +3120,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B97" s="5" t="s">
         <v>6</v>
       </c>
@@ -3153,7 +3153,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B98" s="5" t="s">
         <v>7</v>
       </c>
@@ -3186,7 +3186,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="99" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B99" s="5">
         <v>123</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="100" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B100" s="5" t="s">
         <v>8</v>
       </c>
@@ -3252,7 +3252,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B101" s="5" t="s">
         <v>9</v>
       </c>
@@ -3285,7 +3285,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="102" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B102" s="5" t="s">
         <v>12</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="104" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B104" s="14" t="s">
         <v>42</v>
       </c>
@@ -3332,7 +3332,7 @@
       <c r="J104" s="4"/>
       <c r="K104" s="4"/>
     </row>
-    <row r="105" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B105" s="11" t="s">
         <v>34</v>
       </c>
@@ -3358,7 +3358,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="106" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B106" s="5" t="s">
         <v>4</v>
       </c>
@@ -3391,7 +3391,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="107" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B107" s="5" t="s">
         <v>5</v>
       </c>
@@ -3424,7 +3424,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="108" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B108" s="5" t="s">
         <v>6</v>
       </c>
@@ -3457,7 +3457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B109" s="5" t="s">
         <v>7</v>
       </c>
@@ -3490,7 +3490,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B110" s="5">
         <v>123</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B111" s="5" t="s">
         <v>8</v>
       </c>
@@ -3556,7 +3556,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B112" s="5" t="s">
         <v>9</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="113" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B113" s="5" t="s">
         <v>12</v>
       </c>
@@ -3622,7 +3622,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B115" s="14" t="s">
         <v>43</v>
       </c>
@@ -3636,7 +3636,7 @@
       <c r="J115" s="4"/>
       <c r="K115" s="4"/>
     </row>
-    <row r="116" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B116" s="11" t="s">
         <v>44</v>
       </c>
@@ -3659,7 +3659,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="117" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B117" s="5" t="s">
         <v>4</v>
       </c>
@@ -3688,7 +3688,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B118" s="5" t="s">
         <v>5</v>
       </c>
@@ -3717,7 +3717,7 @@
         <v>Hello</v>
       </c>
     </row>
-    <row r="119" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B119" s="5" t="s">
         <v>6</v>
       </c>
@@ -3746,7 +3746,7 @@
         <v>hello world</v>
       </c>
     </row>
-    <row r="120" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B120" s="5" t="s">
         <v>7</v>
       </c>
@@ -3775,7 +3775,7 @@
         <v xml:space="preserve">  Hello World  </v>
       </c>
     </row>
-    <row r="121" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B121" s="5">
         <v>123</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>ONE23</v>
       </c>
     </row>
-    <row r="122" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B122" s="5" t="s">
         <v>8</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>HelloONE23</v>
       </c>
     </row>
-    <row r="123" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B123" s="5" t="s">
         <v>9</v>
       </c>
@@ -3862,7 +3862,7 @@
         <v>A&amp;B@C</v>
       </c>
     </row>
-    <row r="124" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B124" s="5" t="s">
         <v>12</v>
       </c>
@@ -3897,7 +3897,7 @@
 Break</v>
       </c>
     </row>
-    <row r="126" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B126" s="14" t="s">
         <v>51</v>
       </c>
@@ -3911,7 +3911,7 @@
       <c r="J126" s="4"/>
       <c r="K126" s="4"/>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B127" s="11" t="s">
         <v>52</v>
       </c>
@@ -3931,7 +3931,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="128" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B128" s="5" t="s">
         <v>4</v>
       </c>
@@ -3956,7 +3956,7 @@
         <v>...</v>
       </c>
     </row>
-    <row r="129" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B129" s="5" t="s">
         <v>5</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>Hell...</v>
       </c>
     </row>
-    <row r="130" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B130" s="5" t="s">
         <v>6</v>
       </c>
@@ -4006,7 +4006,7 @@
         <v>hell...</v>
       </c>
     </row>
-    <row r="131" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B131" s="5" t="s">
         <v>7</v>
       </c>
@@ -4031,7 +4031,7 @@
         <v xml:space="preserve">  He...</v>
       </c>
     </row>
-    <row r="132" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B132" s="5">
         <v>123</v>
       </c>
@@ -4056,7 +4056,7 @@
         <v>123...</v>
       </c>
     </row>
-    <row r="133" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B133" s="5" t="s">
         <v>8</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>Hell...</v>
       </c>
     </row>
-    <row r="134" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B134" s="5" t="s">
         <v>9</v>
       </c>
@@ -4106,7 +4106,7 @@
         <v>A&amp;B@...</v>
       </c>
     </row>
-    <row r="135" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B135" s="5" t="s">
         <v>12</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>Line...</v>
       </c>
     </row>
-    <row r="137" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B137" s="14" t="s">
         <v>58</v>
       </c>
@@ -4149,7 +4149,7 @@
       <c r="J137" s="4"/>
       <c r="K137" s="4"/>
     </row>
-    <row r="138" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B138" s="11" t="s">
         <v>59</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="139" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B139" s="5">
         <v>0</v>
       </c>
@@ -4208,7 +4208,7 @@
         <v>Saturday</v>
       </c>
     </row>
-    <row r="140" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B140" s="5">
         <v>1234.5</v>
       </c>
@@ -4241,7 +4241,7 @@
         <v>Monday</v>
       </c>
     </row>
-    <row r="141" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B141" s="5">
         <v>-42.5</v>
       </c>
@@ -4274,7 +4274,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="142" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B142" s="5">
         <v>0.75</v>
       </c>
@@ -4307,7 +4307,7 @@
         <v>Saturday</v>
       </c>
     </row>
-    <row r="143" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B143" s="5">
         <v>44927</v>
       </c>
@@ -4340,7 +4340,7 @@
         <v>Sunday</v>
       </c>
     </row>
-    <row r="144" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B144" s="5">
         <v>0.5</v>
       </c>
@@ -4373,7 +4373,7 @@
         <v>Saturday</v>
       </c>
     </row>
-    <row r="146" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B146" s="4" t="s">
         <v>65</v>
       </c>
@@ -4387,7 +4387,7 @@
       <c r="J146" s="4"/>
       <c r="K146" s="4"/>
     </row>
-    <row r="147" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B147" s="10" t="s">
         <v>2</v>
       </c>
@@ -4395,7 +4395,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="148" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="148" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B148" s="5" t="s">
         <v>38</v>
       </c>
@@ -4404,7 +4404,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="149" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="149" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B149" s="5" t="s">
         <v>67</v>
       </c>
@@ -4413,7 +4413,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="150" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B150" s="5" t="s">
         <v>68</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="151" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B151" s="5" t="s">
         <v>69</v>
       </c>
@@ -4431,7 +4431,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="152" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B152" s="5" t="s">
         <v>70</v>
       </c>
@@ -4440,7 +4440,7 @@
         <v>12300000000</v>
       </c>
     </row>
-    <row r="153" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B153" s="5" t="s">
         <v>71</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="154" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B154" s="5" t="s">
         <v>37</v>
       </c>
@@ -4458,7 +4458,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="155" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="155" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B155" s="5" t="s">
         <v>72</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="157" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="157" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B157" s="14" t="s">
         <v>73</v>
       </c>
@@ -4481,7 +4481,7 @@
       <c r="J157" s="4"/>
       <c r="K157" s="4"/>
     </row>
-    <row r="158" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B158" s="11" t="s">
         <v>74</v>
       </c>
@@ -4501,7 +4501,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B159" s="5" t="s">
         <v>4</v>
       </c>
@@ -4526,7 +4526,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B160" s="5" t="s">
         <v>5</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>HelloHelloHelloHelloHello</v>
       </c>
     </row>
-    <row r="161" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="161" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B161" s="5" t="s">
         <v>6</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>hello worldhello worldhello worldhello worldhello world</v>
       </c>
     </row>
-    <row r="162" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="162" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B162" s="5" t="s">
         <v>7</v>
       </c>
@@ -4601,7 +4601,7 @@
         <v xml:space="preserve">  Hello World    Hello World    Hello World    Hello World    Hello World  </v>
       </c>
     </row>
-    <row r="163" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="163" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B163" s="5">
         <v>123</v>
       </c>
@@ -4626,7 +4626,7 @@
         <v>123123123123123</v>
       </c>
     </row>
-    <row r="164" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="164" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B164" s="5" t="s">
         <v>8</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>Hello123Hello123Hello123Hello123Hello123</v>
       </c>
     </row>
-    <row r="165" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B165" s="5" t="s">
         <v>9</v>
       </c>
@@ -4676,7 +4676,7 @@
         <v>A&amp;B@CA&amp;B@CA&amp;B@CA&amp;B@CA&amp;B@C</v>
       </c>
     </row>
-    <row r="166" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B166" s="5" t="s">
         <v>12</v>
       </c>
@@ -4712,7 +4712,7 @@
 Break</v>
       </c>
     </row>
-    <row r="168" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="168" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B168" s="14" t="s">
         <v>75</v>
       </c>
@@ -4726,7 +4726,7 @@
       <c r="J168" s="4"/>
       <c r="K168" s="4"/>
     </row>
-    <row r="169" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="169" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B169" s="11" t="s">
         <v>1</v>
       </c>
@@ -4755,7 +4755,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="170" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="170" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B170" s="5" t="s">
         <v>4</v>
       </c>
@@ -4792,7 +4792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="171" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B171" s="5" t="s">
         <v>5</v>
       </c>
@@ -4829,7 +4829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="172" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B172" s="5" t="s">
         <v>6</v>
       </c>
@@ -4866,7 +4866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="173" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B173" s="5" t="s">
         <v>7</v>
       </c>
@@ -4903,7 +4903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B174" s="5">
         <v>123</v>
       </c>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="175" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B175" s="5" t="s">
         <v>8</v>
       </c>
@@ -4977,7 +4977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="176" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B176" s="5" t="s">
         <v>9</v>
       </c>
@@ -5014,7 +5014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="177" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B177" s="5" t="s">
         <v>12</v>
       </c>
@@ -5051,7 +5051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B179" s="14" t="s">
         <v>76</v>
       </c>
@@ -5065,7 +5065,7 @@
       <c r="J179" s="4"/>
       <c r="K179" s="4"/>
     </row>
-    <row r="180" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="180" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B180" s="10" t="s">
         <v>77</v>
       </c>
@@ -5080,7 +5080,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="181" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="181" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B181" s="5">
         <v>10</v>
       </c>
@@ -5097,7 +5097,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="182" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="182" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B182" s="5">
         <v>32</v>
       </c>
@@ -5113,7 +5113,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="183" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="183" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B183" s="5">
         <v>48</v>
       </c>
@@ -5129,7 +5129,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="184" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="184" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B184" s="5">
         <v>65</v>
       </c>
@@ -5145,7 +5145,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="185" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="185" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B185" s="5">
         <v>90</v>
       </c>
@@ -5161,7 +5161,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="186" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="186" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B186" s="5">
         <v>97</v>
       </c>
@@ -5177,7 +5177,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="187" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="187" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B187" s="5">
         <v>122</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="188" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="188" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B188" s="5">
         <v>33</v>
       </c>
@@ -5209,7 +5209,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="189" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="189" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B189" s="5">
         <v>64</v>
       </c>
@@ -5225,7 +5225,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="190" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="190" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B190" s="5">
         <v>255</v>
       </c>
